--- a/Excel/2. Mathematical_functios/Mathematical.xlsx
+++ b/Excel/2. Mathematical_functios/Mathematical.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC4103E-E231-4472-9FAB-2EB19A43C360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE0F9AE-CBD8-4450-8591-45CDB7DBD3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUM" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="63">
   <si>
     <t>SUM</t>
   </si>
@@ -211,6 +211,39 @@
   </si>
   <si>
     <t xml:space="preserve"> =SUM(M5:P5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =Relative = Plain</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = Absolute = Row &amp; Column Locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = Mixed = Either row or column anyone should be locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =MIN(M5:M9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =MAX(M5:M9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =AVERAGE(M5:O5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =RANK.AVG(P5,$P$5:$P$9,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =M5*M11+N5*N11+O5*O11</t>
+  </si>
+  <si>
+    <t>Harsh</t>
+  </si>
+  <si>
+    <t>Rehan</t>
+  </si>
+  <si>
+    <t>Manju</t>
   </si>
 </sst>
 </file>
@@ -304,7 +337,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +359,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,7 +501,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -531,7 +576,14 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -586,10 +638,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1469,10 +1517,10 @@
   <sheetData>
     <row r="1" spans="1:28" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="53"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1480,25 +1528,25 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
       <c r="O1" s="15"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
       <c r="AB1" s="15"/>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1507,13 +1555,13 @@
     </row>
     <row r="4" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -1539,11 +1587,11 @@
     </row>
     <row r="5" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -1564,18 +1612,19 @@
         <v>81</v>
       </c>
       <c r="Q5">
+        <f>SUM(M5:P5)</f>
         <v>348</v>
       </c>
-      <c r="S5" t="s">
+      <c r="R5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
@@ -1592,15 +1641,16 @@
         <v>75</v>
       </c>
       <c r="Q6">
+        <f t="shared" ref="Q6:Q9" si="0">SUM(M6:P6)</f>
         <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
@@ -1617,15 +1667,16 @@
         <v>90</v>
       </c>
       <c r="Q7">
+        <f t="shared" si="0"/>
         <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
@@ -1642,15 +1693,16 @@
         <v>85</v>
       </c>
       <c r="Q8">
+        <f t="shared" si="0"/>
         <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
@@ -1667,23 +1719,24 @@
         <v>55</v>
       </c>
       <c r="Q9">
+        <f t="shared" si="0"/>
         <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:28" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -1694,64 +1747,64 @@
     </row>
     <row r="14" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
     </row>
     <row r="15" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1795,10 +1848,10 @@
   <sheetData>
     <row r="1" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="53"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1806,24 +1859,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1832,13 +1885,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -1858,11 +1911,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -1881,107 +1934,110 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
       <c r="M6" s="25">
         <v>65</v>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="35">
         <v>53</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O6" s="34">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
       <c r="M7" s="25">
         <v>85</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="34">
         <v>80</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="34">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
       <c r="M8" s="25">
         <v>99</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="34">
         <v>99</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="34">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="M9" s="33">
+      <c r="M9" s="35">
         <v>45</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="34">
         <v>60</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="35">
         <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
       <c r="L10" s="25" t="s">
         <v>19</v>
       </c>
       <c r="M10">
+        <f>MIN(M5:M9)</f>
         <v>45</v>
       </c>
       <c r="N10">
+        <f t="shared" ref="N10:O10" si="0">MIN(N5:N9)</f>
         <v>53</v>
       </c>
       <c r="O10">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -1989,67 +2045,70 @@
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C13" s="13"/>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2093,10 +2152,10 @@
   <sheetData>
     <row r="1" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="53"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2104,24 +2163,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2130,13 +2189,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -2156,11 +2215,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -2179,11 +2238,11 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
@@ -2198,11 +2257,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
@@ -2212,23 +2271,23 @@
       <c r="N7" s="25">
         <v>80</v>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="36">
         <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="36">
         <v>99</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="36">
         <v>99</v>
       </c>
       <c r="O8" s="25">
@@ -2236,11 +2295,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
@@ -2255,11 +2314,11 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
       <c r="L10" s="25" t="s">
         <v>22</v>
       </c>
@@ -2278,11 +2337,11 @@
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -2290,67 +2349,70 @@
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C13" s="13"/>
+      <c r="M13" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2394,10 +2456,10 @@
   <sheetData>
     <row r="1" spans="1:27" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="53"/>
+      <c r="C1" s="39"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -2405,24 +2467,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2431,13 +2493,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -2463,11 +2525,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -2484,21 +2546,24 @@
       <c r="O5" s="25">
         <v>81</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="37">
         <f>AVERAGE(M5:O5)</f>
         <v>86.333333333333329</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="38">
         <f>_xlfn.RANK.AVG(P5,$P$5:$P$9,0)</f>
         <v>2</v>
       </c>
+      <c r="S5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
@@ -2511,21 +2576,24 @@
       <c r="O6" s="25">
         <v>75</v>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="37">
         <f t="shared" ref="P6:P9" si="0">AVERAGE(M6:O6)</f>
         <v>64.333333333333329</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="38">
         <f t="shared" ref="Q6:Q9" si="1">_xlfn.RANK.AVG(P6,$P$5:$P$9,0)</f>
         <v>4</v>
       </c>
+      <c r="S6" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
@@ -2538,21 +2606,21 @@
       <c r="O7" s="25">
         <v>90</v>
       </c>
-      <c r="P7" s="34">
+      <c r="P7" s="37">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="38">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
@@ -2565,21 +2633,21 @@
       <c r="O8" s="25">
         <v>85</v>
       </c>
-      <c r="P8" s="34">
+      <c r="P8" s="37">
         <f t="shared" si="0"/>
         <v>94.333333333333329</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="38">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
@@ -2592,29 +2660,29 @@
       <c r="O9" s="25">
         <v>55</v>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="37">
         <f t="shared" si="0"/>
         <v>53.333333333333336</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="38">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -2625,64 +2693,73 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="M14" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
+      <c r="M15" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2739,24 +2816,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2765,13 +2842,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -2794,11 +2871,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -2824,11 +2901,11 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
@@ -2847,11 +2924,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
@@ -2870,11 +2947,11 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
@@ -2893,11 +2970,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
@@ -2916,11 +2993,11 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
@@ -2928,11 +3005,11 @@
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
       <c r="L11" s="27" t="s">
         <v>28</v>
       </c>
@@ -2961,7 +3038,9 @@
     <row r="13" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C13" s="13"/>
       <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
+      <c r="M13" s="28" t="s">
+        <v>59</v>
+      </c>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="21"/>
@@ -2969,73 +3048,70 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
       <c r="L14" s="22"/>
-      <c r="M14" s="23">
-        <f>95*2+83*1+81*1.3</f>
-        <v>378.3</v>
-      </c>
+      <c r="M14" s="23"/>
       <c r="N14" s="20"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
       <c r="L15" s="21"/>
       <c r="M15" s="23"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
       <c r="L16" s="21"/>
       <c r="M16" s="23"/>
     </row>
     <row r="17" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
       <c r="L17" s="21"/>
       <c r="M17" s="23"/>
     </row>
     <row r="18" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
       <c r="L18" s="21"/>
       <c r="M18" s="23"/>
     </row>
     <row r="19" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
       <c r="L19" s="21"/>
       <c r="M19" s="21"/>
     </row>
     <row r="20" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
       <c r="N20" s="21"/>
@@ -3044,11 +3120,11 @@
       <c r="Q20" s="21"/>
     </row>
     <row r="21" spans="3:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3102,24 +3178,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -3128,13 +3204,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -3155,11 +3231,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -3179,11 +3255,11 @@
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
@@ -3199,11 +3275,11 @@
       <c r="P6" s="26"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
@@ -3219,11 +3295,11 @@
       <c r="P7" s="26"/>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
@@ -3239,11 +3315,11 @@
       <c r="P8" s="26"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
@@ -3259,11 +3335,11 @@
       <c r="P9" s="26"/>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
@@ -3272,11 +3348,11 @@
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
       <c r="L11" s="31" t="s">
         <v>37</v>
       </c>
@@ -3310,21 +3386,23 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
       <c r="L14" s="25" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M14" s="25">
         <f ca="1">RAND()</f>
-        <v>0.14805081058992964</v>
-      </c>
-      <c r="N14" s="26"/>
+        <v>0.93400988842655575</v>
+      </c>
+      <c r="N14" s="25">
+        <v>0.53049955245849867</v>
+      </c>
       <c r="O14" s="26" t="s">
         <v>45</v>
       </c>
@@ -3332,19 +3410,21 @@
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
       <c r="L15" s="25" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="M15" s="25">
-        <f t="shared" ref="M15:M18" ca="1" si="0">RAND()</f>
-        <v>0.2803588215056122</v>
-      </c>
-      <c r="N15" s="26"/>
+        <f t="shared" ref="M15:M16" ca="1" si="0">RAND()</f>
+        <v>0.31752632490632859</v>
+      </c>
+      <c r="N15" s="25">
+        <v>0.5289045141075559</v>
+      </c>
       <c r="O15" s="26" t="s">
         <v>46</v>
       </c>
@@ -3352,19 +3432,21 @@
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
       <c r="L16" s="25" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" ca="1" si="0"/>
-        <v>0.38046909980860322</v>
-      </c>
-      <c r="N16" s="26"/>
+        <v>0.24290960972199327</v>
+      </c>
+      <c r="N16" s="25">
+        <v>0.65873943277894387</v>
+      </c>
       <c r="O16" s="26"/>
       <c r="P16" s="26"/>
       <c r="Q16">
@@ -3372,18 +3454,13 @@
       </c>
     </row>
     <row r="17" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
-      <c r="L17" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="M17" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>5.2495980611045101E-2</v>
-      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
       <c r="N17" s="26"/>
       <c r="O17" s="26"/>
       <c r="P17" s="26"/>
@@ -3392,28 +3469,23 @@
       </c>
     </row>
     <row r="18" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
-      <c r="L18" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" s="25">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.73949368364446866</v>
-      </c>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
       <c r="N18" s="26"/>
       <c r="O18" s="26"/>
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
       <c r="L19" s="26"/>
       <c r="M19" s="26"/>
       <c r="N19" s="26"/>
@@ -3421,11 +3493,11 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
       <c r="N20" s="26"/>
@@ -3433,11 +3505,11 @@
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="3:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
       <c r="L21" s="26"/>
       <c r="M21" s="26"/>
       <c r="N21" s="26"/>
@@ -3497,24 +3569,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -3523,13 +3595,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -3549,11 +3621,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -3570,16 +3642,16 @@
       <c r="O5" s="25">
         <v>81</v>
       </c>
-      <c r="R5" s="54">
+      <c r="R5" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
       <c r="L6" s="25" t="s">
         <v>31</v>
       </c>
@@ -3594,11 +3666,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
       <c r="L7" s="25" t="s">
         <v>32</v>
       </c>
@@ -3613,11 +3685,11 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
       <c r="L8" s="25" t="s">
         <v>33</v>
       </c>
@@ -3633,11 +3705,11 @@
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
       <c r="L9" s="25" t="s">
         <v>34</v>
       </c>
@@ -3652,34 +3724,34 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
       <c r="L10" s="33" t="s">
         <v>39</v>
       </c>
       <c r="M10" s="26">
-        <f ca="1">RANDBETWEEN(45,95)</f>
-        <v>61</v>
+        <f ca="1">RANDBETWEEN(35,80)</f>
+        <v>77</v>
       </c>
       <c r="N10" s="26">
-        <f t="shared" ref="N10:O10" ca="1" si="0">RANDBETWEEN(45,95)</f>
-        <v>69</v>
+        <f t="shared" ref="N10:O10" ca="1" si="0">RANDBETWEEN(35,80)</f>
+        <v>70</v>
       </c>
       <c r="O10" s="26">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="43"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
       <c r="N11" s="26"/>
       <c r="O11" s="26"/>
     </row>
@@ -3699,23 +3771,23 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
       <c r="N14" s="26"/>
       <c r="O14" s="26"/>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
       <c r="M15" t="s">
         <v>48</v>
       </c>
@@ -3724,54 +3796,54 @@
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
       <c r="N16" s="26"/>
       <c r="O16" s="26"/>
     </row>
     <row r="17" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="47"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
       <c r="N17" s="26"/>
       <c r="O17" s="26"/>
     </row>
     <row r="18" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="47"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
       <c r="N18" s="26"/>
       <c r="O18" s="26"/>
     </row>
     <row r="19" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
       <c r="N19" s="26"/>
       <c r="O19" s="26"/>
     </row>
     <row r="20" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="47"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="3:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="52"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3825,24 +3897,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
